--- a/data/rateBuildUp/RebateRefreshOutput/RBU_Execution_Summary26Jun.xlsx
+++ b/data/rateBuildUp/RebateRefreshOutput/RBU_Execution_Summary26Jun.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>18</v>
